--- a/api/src/excelreports/reportTemplates/Reports.xlsx
+++ b/api/src/excelreports/reportTemplates/Reports.xlsx
@@ -157,9 +157,6 @@
     <t>&lt;error&gt;</t>
   </si>
   <si>
-    <t>Total Test Run</t>
-  </si>
-  <si>
     <t>Total Errors</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>&lt;totalErrors&gt;</t>
+  </si>
+  <si>
+    <t>Total Tests Run</t>
   </si>
 </sst>
 </file>
@@ -831,10 +831,10 @@
         <v>40</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>44</v>
       </c>
       <c r="E5" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
